--- a/r5-aist-trustworthyai-poc-pipeline/ValueSet-eu-ai-data-quality-vs.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/ValueSet-eu-ai-data-quality-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Attributes describing the quality of training data.</t>
+    <t>Codes describing data-quality characteristics relevant for training-data documentation (Art. 10 AI Act).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>complete</t>
+  </si>
+  <si>
+    <t>relevant</t>
   </si>
   <si>
     <t>System URI</t>
@@ -364,7 +367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -399,18 +402,24 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
         <v>31</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
